--- a/docs/app01.file/人工智能学院通讯录(1).xlsx
+++ b/docs/app01.file/人工智能学院通讯录(1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>人工智能学院教师名单</t>
   </si>
@@ -86,9 +86,6 @@
     <t>刘婷婷</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>钟紫绢</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>王晓寒</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>聂子凡</t>
   </si>
   <si>
@@ -123,9 +117,6 @@
   </si>
   <si>
     <t>黄晓东</t>
-  </si>
-  <si>
-    <t>c</t>
   </si>
   <si>
     <t>秦 天</t>
@@ -1077,7 +1068,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1092,9 +1083,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1697,427 +1685,413 @@
       <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" ht="17.5" spans="1:4">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="5"/>
-      <c r="D3" s="6"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" ht="17.5" spans="1:4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" ht="17.5" spans="1:4">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
+      <c r="D5" s="5"/>
     </row>
     <row r="6" ht="17.5" spans="1:4">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" ht="17.5" spans="1:4">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" ht="17.5" spans="1:4">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" ht="17.5" spans="1:4">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="6"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" ht="17.5" spans="1:4">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="5"/>
-      <c r="D10" s="6"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" ht="17.5" spans="1:4">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="5"/>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" ht="17.5" spans="1:4">
+      <c r="A12" s="10"/>
+      <c r="B12" s="9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" ht="17.5" spans="1:4">
-      <c r="A12" s="11"/>
-      <c r="B12" s="10" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" ht="17.5" spans="1:4">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" ht="17.5" spans="1:4">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" ht="17.5" spans="1:4">
+      <c r="A14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" ht="17.5" spans="1:4">
-      <c r="A14" s="9" t="s">
+      <c r="B14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" ht="17.5" spans="1:4">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" ht="17.5" spans="1:4">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" ht="17.5" spans="1:4">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" ht="17.5" spans="1:4">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12" t="s">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" ht="17.5" spans="1:4">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6" t="s">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" ht="17.5" spans="1:4">
+      <c r="A18" s="12"/>
+      <c r="B18" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" ht="17.5" spans="1:4">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12" t="s">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" ht="17.5" spans="1:4">
+      <c r="A19" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" ht="17.5" spans="1:4">
-      <c r="A18" s="13"/>
-      <c r="B18" s="12" t="s">
+      <c r="B19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" ht="17.5" spans="1:4">
-      <c r="A19" s="9" t="s">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" ht="17.5" spans="1:4">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" ht="17.5" spans="1:4">
+      <c r="A21" s="12"/>
+      <c r="B21" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" ht="17.5" spans="1:4">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12" t="s">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" ht="17.5" spans="1:4">
+      <c r="A22" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="6" t="s">
+      <c r="B22" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" ht="17.5" spans="1:4">
-      <c r="A21" s="13"/>
-      <c r="B21" s="12" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" ht="17.5" spans="1:4">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22" ht="17.5" spans="1:4">
-      <c r="A22" s="9" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" ht="17.5" spans="1:4">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" ht="17.5" spans="1:4">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" ht="17.5" spans="1:4">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" ht="17.5" spans="1:4">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" ht="17.5" spans="1:4">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12" t="s">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" ht="17.5" spans="1:4">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" ht="17.5" spans="1:4">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" ht="17.5" spans="1:4">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" ht="17.5" spans="1:4">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12" t="s">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" ht="17.5" spans="1:4">
+      <c r="A29" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" ht="17.5" spans="1:4">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12" t="s">
+      <c r="B29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="6"/>
-    </row>
-    <row r="28" ht="17.5" spans="1:4">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" ht="17.5" spans="1:4">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="6"/>
-    </row>
-    <row r="29" ht="17.5" spans="1:4">
-      <c r="A29" s="11" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" ht="17.5" spans="1:4">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" ht="17.5" spans="1:4">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" ht="17.5" spans="1:4">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12" t="s">
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" ht="17.5" spans="1:4">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" ht="17.5" spans="1:4">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12" t="s">
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" ht="17.5" spans="1:4">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="6"/>
-    </row>
-    <row r="32" ht="17.5" spans="1:4">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12" t="s">
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" ht="17.5" spans="1:4">
+      <c r="A35" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="6"/>
-    </row>
-    <row r="33" ht="17.5" spans="1:4">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12" t="s">
+      <c r="B35" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="6"/>
-    </row>
-    <row r="34" ht="17.5" spans="1:4">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12" t="s">
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" ht="17.5" spans="1:4">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="6"/>
-    </row>
-    <row r="35" ht="17.5" spans="1:4">
-      <c r="A35" s="15" t="s">
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" ht="17.5" spans="1:4">
+      <c r="A37" s="14"/>
+      <c r="B37" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" ht="17.5" spans="1:4">
+      <c r="A38" s="14"/>
+      <c r="B38" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="6"/>
-    </row>
-    <row r="36" ht="17.5" spans="1:4">
-      <c r="A36" s="15"/>
-      <c r="B36" s="16" t="s">
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" ht="17.5" spans="1:4">
+      <c r="A39" s="14"/>
+      <c r="B39" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="6"/>
-    </row>
-    <row r="37" ht="17.5" spans="1:4">
-      <c r="A37" s="15"/>
-      <c r="B37" s="16" t="s">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" ht="17.5" spans="1:4">
+      <c r="A40" s="14"/>
+      <c r="B40" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="6"/>
-    </row>
-    <row r="38" ht="17.5" spans="1:4">
-      <c r="A38" s="15"/>
-      <c r="B38" s="17" t="s">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" ht="17.5" spans="1:4">
+      <c r="A41" s="14"/>
+      <c r="B41" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="6"/>
-    </row>
-    <row r="39" ht="17.5" spans="1:4">
-      <c r="A39" s="15"/>
-      <c r="B39" s="16" t="s">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" ht="17.5" spans="1:4">
+      <c r="A42" s="14"/>
+      <c r="B42" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="6"/>
-    </row>
-    <row r="40" ht="17.5" spans="1:4">
-      <c r="A40" s="15"/>
-      <c r="B40" s="16" t="s">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" ht="17.5" spans="1:4">
+      <c r="A43" s="14"/>
+      <c r="B43" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" ht="17.5" spans="1:4">
-      <c r="A41" s="15"/>
-      <c r="B41" s="16" t="s">
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" ht="17.5" spans="1:4">
+      <c r="A44" s="14"/>
+      <c r="B44" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="6"/>
-    </row>
-    <row r="42" ht="17.5" spans="1:4">
-      <c r="A42" s="15"/>
-      <c r="B42" s="16" t="s">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" ht="17.5" spans="1:4">
+      <c r="A45" s="14"/>
+      <c r="B45" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" ht="17.5" spans="1:4">
-      <c r="A43" s="15"/>
-      <c r="B43" s="16" t="s">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" ht="17.5" spans="1:4">
+      <c r="A46" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" ht="17.5" spans="1:4">
-      <c r="A44" s="15"/>
-      <c r="B44" s="16" t="s">
+      <c r="B46" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" ht="17.5" spans="1:4">
-      <c r="A45" s="15"/>
-      <c r="B45" s="16" t="s">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" ht="17.5" spans="1:4">
+      <c r="A47" s="14"/>
+      <c r="B47" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" ht="17.5" spans="1:4">
-      <c r="A46" s="15" t="s">
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" ht="17.5" spans="1:4">
+      <c r="A48" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B48" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="6"/>
-    </row>
-    <row r="47" ht="17.5" spans="1:4">
-      <c r="A47" s="15"/>
-      <c r="B47" s="18" t="s">
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+    </row>
+    <row r="49" ht="22" customHeight="1" spans="1:4">
+      <c r="A49" s="14"/>
+      <c r="B49" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="6"/>
-    </row>
-    <row r="48" ht="17.5" spans="1:4">
-      <c r="A48" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="6"/>
-    </row>
-    <row r="49" ht="22" customHeight="1" spans="1:4">
-      <c r="A49" s="15"/>
-      <c r="B49" s="19" t="s">
-        <v>66</v>
-      </c>
       <c r="C49" s="5"/>
-      <c r="D49" s="6"/>
+      <c r="D49" s="5"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
